--- a/看板数据溯源映射表.xlsx
+++ b/看板数据溯源映射表.xlsx
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1194,86 +1194,78 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>项目进度分布</t>
+          <t>人员工作饱和度分析</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>各进度区间项目数</t>
+          <t>在岗人员数</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>区间COUNT</t>
+          <t>COUNT</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>项目数据表.xlsx</t>
+          <t>人力投入表.xlsx</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>项目状态信息</t>
+          <t>人员档案台账</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>项目进度</t>
+          <t>实际投入工时、所属中心</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>项目进度&gt;0</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>排除0值，6个区间</t>
-        </is>
-      </c>
+          <t>所属中心="数智技术服务中心" 且 实际投入工时&gt;0</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>本月部门人力投入</t>
+          <t>人员工作饱和度分析</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>各部门投入人月</t>
+          <t>未投入人员数</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>GROUPBY SUM</t>
+          <t>COUNT</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>项目数据表.xlsx</t>
+          <t>人力投入表.xlsx</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>项目状态信息</t>
+          <t>人员档案台账</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>所属部门、本月投入人力（人月）</t>
+          <t>实际投入工时、所属中心</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>本月投入人力（人月）&gt;0 且 所属部门∈数智技术服务中心</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>部门名映射：智能部→智能技术一部/二部等</t>
-        </is>
-      </c>
+          <t>所属中心="数智技术服务中心" 且 实际投入工时=0</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1283,12 +1275,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>在岗人员数</t>
+          <t>整体饱和度</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COUNT</t>
+          <t>在岗合计实际工时/全部应投入工时</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -1303,15 +1295,19 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>实际投入工时、所属中心</t>
+          <t>实际投入工时、应投入工时、所属中心</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>所属中心="数智技术服务中心" 且 实际投入工时&gt;0</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr"/>
+          <t>所属中心="数智技术服务中心"</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>不显示实际工时数值</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -1321,12 +1317,12 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>未投入人员数</t>
+          <t>饱和度分布饼图</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>COUNT</t>
+          <t>区间COUNT</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -1341,30 +1337,34 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>实际投入工时、所属中心</t>
+          <t>工作饱和度、所属中心</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>所属中心="数智技术服务中心" 且 实际投入工时=0</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr"/>
+          <t>所属中心="数智技术服务中心"</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>6个区间：≥90%/70-90%/50-70%/10-50%/&lt;10%/无投入</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>人员工作饱和度分析</t>
+          <t>部门工时投入对比</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>整体饱和度</t>
+          <t>各部门实际工时</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>在岗合计实际工时/全部应投入工时</t>
+          <t>GROUPBY SUM</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>实际投入工时、应投入工时、所属中心</t>
+          <t>实际投入工时、所属中心、部门</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1389,24 +1389,24 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>不显示实际工时数值</t>
+          <t>分组柱状图：实际 vs 应投入</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>人员工作饱和度分析</t>
+          <t>部门工时投入对比</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>饱和度分布饼图</t>
+          <t>各部门应投入工时</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>区间COUNT</t>
+          <t>GROUPBY SUM</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>工作饱和度、所属中心</t>
+          <t>应投入工时、所属中心、部门</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
@@ -1429,26 +1429,22 @@
           <t>所属中心="数智技术服务中心"</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>6个区间：≥90%/70-90%/50-70%/10-50%/&lt;10%/无投入</t>
-        </is>
-      </c>
+      <c r="H23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>部门工时投入对比</t>
+          <t>部门人均工作饱和度</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>各部门实际工时</t>
+          <t>各部门人均饱和度</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>GROUPBY SUM</t>
+          <t>部门实际工时合计/部门应投入工时合计</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -1463,7 +1459,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>实际投入工时、所属中心、部门</t>
+          <t>实际投入工时、应投入工时、所属中心、部门</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1473,104 +1469,108 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>分组柱状图：实际 vs 应投入</t>
+          <t>按部门GROUPBY后计算</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>部门工时投入对比</t>
+          <t>本期人力投入TOP10</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>各部门应投入工时</t>
+          <t>TOP10项目各部门投入</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>GROUPBY SUM</t>
+          <t>TOP10 + 部门拆分</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>人力投入表.xlsx</t>
+          <t>本期人力投入项目情况(2026-03-01开始截至2026-03-31).xlsx</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>人员档案台账</t>
+          <t>本期人力投入项目情况</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>应投入工时、所属中心、部门</t>
+          <t>项目名称、智能部、政务部、大数据部、产品创新部、其他部门投入、本期总投入（人月）</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>所属中心="数智技术服务中心"</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr"/>
+          <t>按本期总投入（人月）降序取前10</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>堆叠柱状图按部门着色</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>部门人均工作饱和度</t>
+          <t>各部门人力投入TOP3</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>各部门人均饱和度</t>
+          <t>智能部TOP3</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>部门实际工时合计/部门应投入工时合计</t>
+          <t>NLARGEST</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>人力投入表.xlsx</t>
+          <t>本期人力投入项目情况.xlsx</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>人员档案台账</t>
+          <t>本期人力投入项目情况</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>实际投入工时、应投入工时、所属中心、部门</t>
+          <t>项目名称、智能部、本期总投入（人月）</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>所属中心="数智技术服务中心"</t>
+          <t>智能部&gt;0</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>按部门GROUPBY后计算</t>
+          <t>按智能部投入降序取前3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>本期人力投入TOP10</t>
+          <t>各部门人力投入TOP3</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>TOP10项目各部门投入</t>
+          <t>政务部TOP3</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>TOP10 + 部门拆分</t>
+          <t>NLARGEST</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -1585,17 +1585,17 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>项目名称、智能部、政务部、大数据部、产品创新部、其他部门投入、本期总投入（人月）</t>
+          <t>项目名称、政务部、本期总投入（人月）</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>按本期总投入（人月）降序取前10</t>
+          <t>政务部&gt;0</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>堆叠柱状图按部门着色</t>
+          <t>按政务部投入降序取前3</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>智能部TOP3</t>
+          <t>大数据部TOP3</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1627,17 +1627,17 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>项目名称、智能部、本期总投入（人月）</t>
+          <t>项目名称、大数据部、本期总投入（人月）</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>智能部&gt;0</t>
+          <t>大数据部&gt;0</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>按智能部投入降序取前3</t>
+          <t>按大数据部投入降序取前3</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>政务部TOP3</t>
+          <t>产品创新部TOP3</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1669,113 +1669,105 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>项目名称、政务部、本期总投入（人月）</t>
+          <t>项目名称、产品创新部、本期总投入（人月）</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>政务部&gt;0</t>
+          <t>产品创新部&gt;0</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>按政务部投入降序取前3</t>
+          <t>按产品创新部投入降序取前3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>各部门人力投入TOP3</t>
+          <t>本期项目变化动态</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>大数据部TOP3</t>
+          <t>新增项目列表</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>NLARGEST</t>
+          <t>FILTER</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>本期人力投入项目情况.xlsx</t>
+          <t>本期项目变化情况.xlsx</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>本期人力投入项目情况</t>
+          <t>项目变化</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>项目名称、大数据部、本期总投入（人月）</t>
+          <t>操作日期、项目名称、项目经理、计划开始日期、计划完成日期、类型</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>大数据部&gt;0</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>按大数据部投入降序取前3</t>
-        </is>
-      </c>
+          <t>类型="新增项目"</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>各部门人力投入TOP3</t>
+          <t>本期项目变化动态</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>产品创新部TOP3</t>
+          <t>延期项目列表</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>NLARGEST</t>
+          <t>FILTER</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>本期人力投入项目情况.xlsx</t>
+          <t>本期项目变化情况.xlsx</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>本期人力投入项目情况</t>
+          <t>项目变化</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>项目名称、产品创新部、本期总投入（人月）</t>
+          <t>操作日期、项目名称、项目经理、计划开始日期、计划完成日期、类型</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>产品创新部&gt;0</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>按产品创新部投入降序取前3</t>
-        </is>
-      </c>
+          <t>类型="延期项目"</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>本期项目变化动态</t>
+          <t>项目超期/到期预警</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>新增项目列表</t>
+          <t>已超期项目</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1785,22 +1777,22 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>本期项目变化情况.xlsx</t>
+          <t>本期人力投入项目情况.xlsx</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>项目变化</t>
+          <t>本期人力投入项目情况</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>操作日期、项目名称、项目经理、计划开始日期、计划完成日期、类型</t>
+          <t>项目名称、所属部门、禅道是否超期/到期、中心人力投入（人月）</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>类型="新增项目"</t>
+          <t>禅道是否超期/到期 包含"超期"</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
@@ -1808,12 +1800,12 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>本期项目变化动态</t>
+          <t>项目超期/到期预警</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>延期项目列表</t>
+          <t>60天内到期项目</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -1823,135 +1815,143 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>本期项目变化情况.xlsx</t>
+          <t>本期人力投入项目情况.xlsx</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>项目变化</t>
+          <t>本期人力投入项目情况</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>操作日期、项目名称、项目经理、计划开始日期、计划完成日期、类型</t>
+          <t>项目名称、所属部门、禅道是否超期/到期、中心人力投入（人月）</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>类型="延期项目"</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr"/>
+          <t>禅道是否超期/到期 包含"还有" 且 天数≤60</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>提取"还有X天"中的X</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>项目超期/到期预警</t>
+          <t>合同金额TOP10</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>已超期项目</t>
+          <t>TOP10项目</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>FILTER</t>
+          <t>NLARGEST</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>本期人力投入项目情况.xlsx</t>
+          <t>项目数据表.xlsx</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>本期人力投入项目情况</t>
+          <t>项目状态信息</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>项目名称、所属部门、禅道是否超期/到期、中心人力投入（人月）</t>
+          <t>项目名称、合同金额（元）、已回款金额（元）、合同回款情况、所属部门、项目阶段、项目进度</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>禅道是否超期/到期 包含"超期"</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr"/>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>按合同金额降序取前10</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>项目超期/到期预警</t>
+          <t>人力投入累计TOP10</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>60天内到期项目</t>
+          <t>TOP10项目</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>FILTER</t>
+          <t>NLARGEST</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>本期人力投入项目情况.xlsx</t>
+          <t>项目数据表.xlsx</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>本期人力投入项目情况</t>
+          <t>项目状态信息</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>项目名称、所属部门、禅道是否超期/到期、中心人力投入（人月）</t>
+          <t>项目名称、累计投入工作量（人月）、所属部门、项目经理</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>禅道是否超期/到期 包含"还有" 且 天数≤60</t>
+          <t>无</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>提取"还有X天"中的X</t>
+          <t>按累计投入降序取前10</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>合同金额TOP10</t>
+          <t>本期人力投入项目明细</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>TOP10项目</t>
+          <t>全部项目明细</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>NLARGEST</t>
+          <t>全量</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>项目数据表.xlsx</t>
+          <t>本期人力投入项目情况.xlsx</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>项目状态信息</t>
+          <t>本期人力投入项目情况</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>项目名称、合同金额（元）、已回款金额（元）、合同回款情况、所属部门、项目阶段、项目进度</t>
+          <t>项目名称、所属部门、中心人力投入（人月）、智能部、政务部、大数据部、产品创新部、其他部门投入、本期总投入（人月）、禅道是否超期/到期</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1961,24 +1961,24 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>按合同金额降序取前10</t>
+          <t>按本期总投入降序排列</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>人力投入累计TOP10</t>
+          <t>挂起项目</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>TOP10项目</t>
+          <t>挂起项目列表</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>NLARGEST</t>
+          <t>FILTER</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -1993,137 +1993,53 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>项目名称、累计投入工作量（人月）、所属部门、项目经理</t>
+          <t>项目名称、合同金额（元）、所属部门、项目经理、项目进度</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>按累计投入降序取前10</t>
-        </is>
-      </c>
+          <t>项目阶段="挂起"</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>本期人力投入项目明细</t>
+          <t>低饱和度人员</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>全部项目明细</t>
+          <t>低饱和度人员列表</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>全量</t>
+          <t>FILTER</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>本期人力投入项目情况.xlsx</t>
+          <t>人力投入表.xlsx</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>本期人力投入项目情况</t>
+          <t>人员档案台账</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>项目名称、所属部门、中心人力投入（人月）、智能部、政务部、大数据部、产品创新部、其他部门投入、本期总投入（人月）、禅道是否超期/到期</t>
+          <t>姓名、部门、实际投入工时、应投入工时、工作饱和度、岗位</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>按本期总投入降序排列</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>挂起项目</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>挂起项目列表</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>FILTER</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>项目数据表.xlsx</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>项目状态信息</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>项目名称、合同金额（元）、所属部门、项目经理、项目进度</t>
-        </is>
-      </c>
-      <c r="G39" s="4" t="inlineStr">
-        <is>
-          <t>项目阶段="挂起"</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>低饱和度人员</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>低饱和度人员列表</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>FILTER</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>人力投入表.xlsx</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>人员档案台账</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>姓名、部门、实际投入工时、应投入工时、工作饱和度、岗位</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
           <t>所属中心="数智技术服务中心" 且 工作饱和度&lt;0.5 且 实际投入工时&gt;0</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
